--- a/Notes/notes-WILD_kanto_water.xlsx
+++ b/Notes/notes-WILD_kanto_water.xlsx
@@ -1,426 +1,3 @@
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868A12E0-C66B-42AC-B191-1223DC0BEB29}">
-  <dimension ref="A1:N19"/>
-  <sheetFormatPr defaultColWidth="10.7109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="4.7109375" style="4" customWidth="1"/>
-    <col min="2" max="2" width="2.7109375" style="3" customWidth="1"/>
-    <col min="3" max="6" width="11.7109375" style="4" customWidth="1"/>
-    <col min="7" max="7" width="2.7109375" style="3" customWidth="1"/>
-    <col min="8" max="13" width="11.7109375" style="4" customWidth="1"/>
-    <col min="14" max="14" width="2.7109375" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="10.7109375" style="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1">
-        <v>33</v>
-      </c>
-      <c r="F1" s="1"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <f>SUM(C2:F2)</f>
-        <v>0</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9"/>
-      <c r="H2" s="9">
-        <v>100</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="9"/>
-      <c r="M2" s="9"/>
-    </row>
-    <row r="3" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <f>SUM(C3:F3)</f>
-        <v>0</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="12">
-        <v>50</v>
-      </c>
-      <c r="J3" s="11">
-        <v>50</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
-      <c r="M3" s="11"/>
-    </row>
-    <row r="4" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <f>SUM(C4:F4)</f>
-        <v>100</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="5">
-        <v>60</v>
-      </c>
-      <c r="D4" s="6">
-        <v>30</v>
-      </c>
-      <c r="E4" s="6">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="K4" s="14">
-        <v>33</v>
-      </c>
-      <c r="L4" s="14">
-        <v>33</v>
-      </c>
-      <c r="M4" s="5">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="L5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1">
-        <f>SUM(C7:C11)</f>
-        <v>60</v>
-      </c>
-      <c r="D6" s="1">
-        <f>SUM(D7:D11)</f>
-        <v>30</v>
-      </c>
-      <c r="E6" s="1">
-        <f>SUM(E7:E11)</f>
-        <v>10</v>
-      </c>
-      <c r="F6" s="1">
-        <f>SUM(F7:F11)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <f t="shared" ref="H6:M6" si="0">SUM(H7:H11)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="1">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>50</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="8">
-        <v>50</v>
-      </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>30</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="D8" s="7">
-        <v>30</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>10</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="7">
-        <v>10</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-    </row>
-    <row r="10" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>10</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8">
-        <v>10</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-    </row>
-    <row r="11" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-    </row>
-    <row r="12" spans="1:13" s="3" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="1">
-        <f>SUM(C7:C11)</f>
-        <v>60</v>
-      </c>
-      <c r="D12" s="1">
-        <f>SUM(D7:D11)</f>
-        <v>30</v>
-      </c>
-      <c r="E12" s="1">
-        <f>SUM(E7:E11)</f>
-        <v>10</v>
-      </c>
-      <c r="F12" s="1">
-        <f>SUM(F7:F11)</f>
-        <v>0</v>
-      </c>
-      <c r="H12" s="1">
-        <f t="shared" ref="H12:M12" si="1">SUM(H7:H11)</f>
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1">
-        <v>33</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-    </row>
-    <row r="14" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C14" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <f>SUM(C15:F15)</f>
-        <v>100</v>
-      </c>
-      <c r="C15" s="9">
-        <v>60</v>
-      </c>
-      <c r="D15" s="10">
-        <v>30</v>
-      </c>
-      <c r="E15" s="10">
-        <v>10</v>
-      </c>
-      <c r="F15" s="9"/>
-      <c r="H15" s="9">
-        <v>85</v>
-      </c>
-      <c r="I15" s="10">
-        <v>15</v>
-      </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-    </row>
-    <row r="16" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <f>SUM(C16:F16)</f>
-        <v>0</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="11"/>
-      <c r="H16" s="11">
-        <v>35</v>
-      </c>
-      <c r="I16" s="12">
-        <v>65</v>
-      </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-    </row>
-    <row r="17" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <f>SUM(C17:F17)</f>
-        <v>0</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="5"/>
-      <c r="H17" s="5">
-        <v>20</v>
-      </c>
-      <c r="I17" s="6">
-        <v>70</v>
-      </c>
-      <c r="J17" s="5">
-        <v>10</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="5"/>
-      <c r="M17" s="5"/>
-    </row>
-    <row r="19" spans="1:13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C19" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:A4">
-    <cfRule type="cellIs" dxfId="17" priority="2" operator="notEqual">
-      <formula>100</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15:A17">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="notEqual">
-      <formula>100</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8489A5B0-C57D-4D41-AF85-9C47DDC91AFE}">
